--- a/光伏配储项目/电价数据/2026/康州站.xlsx
+++ b/光伏配储项目/电价数据/2026/康州站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51018</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.95931</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.6971900000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.71182</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.54225</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45431</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42302</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44386</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25399</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09972</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11132</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09827</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12251</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.17094</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06177000000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09062000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.2124</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.10071</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.26062</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.64032</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22668</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.18564</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.05356</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.60397</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27549</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.73375</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19694</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.7461</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.88307</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.46291</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.53163</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.40593</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.47084</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.72014</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.61293</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.56271</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5749500000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46432</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.62149</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8121900000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.65685</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63093</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.76818</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.02383</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.48262</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6777799999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.55577</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7517999999999999</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.56014</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.54886</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.64363</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.61564</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47394</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47276</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42568</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69951</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.33076</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.72651</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.2278</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.76435</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5246799999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5188200000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5091</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46996</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39123</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5942000000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.67822</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42997</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51567</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.05773</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.82852</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.8512799999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.82474</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.80584</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.73993</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.6699299999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5797599999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.47565</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.10692</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.69442</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5049399999999999</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.13117</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.78932</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.75986</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.9589500000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8164600000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.63812</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.66311</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42755</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.41284</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5842000000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.71163</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.57568</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6946</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7484</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7214700000000001</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.5788099999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.5314500000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.71866</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.5373300000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.84635</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.10711</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.68925</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.8935299999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.82372</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.54969</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.54206</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.65991</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.71193</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.4401600000000001</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33457</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1.07408</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.64761</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44718</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.48085</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.00682</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.54204</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.5714199999999999</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47385</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.56733</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.5610599999999999</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.47509</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20851</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26735</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47552</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.48129</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.52151</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48617</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16213</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27247</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28188</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.49462</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43305</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.42724</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.54247</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.62173</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.63785</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.89724</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.47782</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50301</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44369</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46425</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.42894</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40434</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34239</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.5055299999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.24081</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.2235</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.45796</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.8581299999999999</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.80826</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.13107</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6283200000000001</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.81159</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.0391</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.81309</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.26779</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.08120999999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.6299600000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.7972</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.34943</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06594</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29232</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.26558</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23992</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.25351</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.22728</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14055</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.58457</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46687</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.45756</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.44901</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.49248</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.5460900000000001</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.49349</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.46771</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29882</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.2605</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04751</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.17582</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04806000000000001</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03371</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04692</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04159</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04047</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04054</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04096</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03947</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04176</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04246</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04117</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04258</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.0459</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04692</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21878</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05357</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05634</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.0008100000000000001</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.06886</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.42602</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39213</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46761</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35099</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.98698</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44663</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10253</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04609000000000001</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03673</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04291</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10505</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00102</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04065999999999999</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04969</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04547</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04344</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04311</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.0418</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04405</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.0417</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04362</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04727000000000001</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04765</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2001</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14298</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29835</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33571</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3179</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28827</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28115</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28129</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17257</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15881</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17114</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14787</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15961</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15878</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22674</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26907</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28597</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45444</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15647</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220599999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78104</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92045</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9160499999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8681599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2993</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89295</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63261</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19246</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8714500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.54611</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33632</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03669</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79557</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53066</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7776000000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7812</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87734</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87627</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49746</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40546</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21257</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8790399999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55115</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62738</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53971</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49931</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45653</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43815</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41485</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45085</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58687</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59613</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60253</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.67196</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58087</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45195</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88113</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63473</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.15488</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.13673</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86349</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44265</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.86314</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>1.13345</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.7335</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45274</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35351</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9257000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46766</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.48069</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38789</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.26168</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16532</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.26722</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.03199</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26233</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19917</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.11771</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.26506</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.26026</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27639</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5974299999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8905299999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.26031</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.26823</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.26726</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.27149</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.27697</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.15409</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26759</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26359</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57378</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32418</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.29248</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.25752</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.24094</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.25895</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.23288</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.26128</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.26184</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.26064</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.26032</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26101</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.69728</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.71839</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26053</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>1.03361</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04757</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.26179</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.25939</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25983</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.26019</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.25789</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.25686</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.25943</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.34921</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34896</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.25431</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.23518</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28169</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.23404</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26422</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19851</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24824</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24097</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26821</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.25234</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.25233</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.25208</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2403</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.23506</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.64462</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.33014</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4971</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29612</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25033</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.7191900000000001</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22642</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6699400000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49394</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26006</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2879</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.86238</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.25263</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.27937</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34961</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28025</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.27921</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.28005</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.28055</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.37676</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33675</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.28098</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.28106</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26466</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14341</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28573</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19993</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26021</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22122</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27022</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2795899999999999</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14733</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.4371</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.56026</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.03094</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.7143400000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6666599999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.8537899999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.9266</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44723</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47493</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40942</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47642</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36011</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48996</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5017699999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46136</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.4670299999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.15416</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.28518</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>-0.04109</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>-0.04406</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.13424</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.14222</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.13996</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28947</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6450499999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.16858</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.15024</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>-0.03507</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.13439</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.36244</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48548</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.8292</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.8588899999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.65139</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.72096</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8087300000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5678</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.49299</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.73136</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.68171</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61793</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.63518</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47583</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47781</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44486</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5410900000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42949</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44128</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44313</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.43535</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44034</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.37589</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>-0.0377</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4647</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11466</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18108</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.43048</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41445</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36569</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39601</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22796</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23049</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25031</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26033</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14016</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25226</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25129</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16995</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18288</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22903</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25026</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26515</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23263</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27566</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35039</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26063</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17777</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.22139</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02265</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04932</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11997</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03931</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01441</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03949</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0365</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04787</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04737</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02428</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02604</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04937</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.12854</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04934</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04917</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04936</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.0298</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04933</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04919</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04134</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18445</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.21237</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2481</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27523</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27692</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42309</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30561</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.18592</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.64995</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.45823</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.21841</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.26736</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.25233</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.26531</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.27451</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.29624</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.25577</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21486</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.70461</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.7097</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.70812</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.65495</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.20086</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12199</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.2541</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.21402</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.16533</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.16893</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.13367</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23889</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.15378</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.04829</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.09813</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.14167</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.20007</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0202</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.16352</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.17059</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.18234</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.00076</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.14634</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.15472</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.15418</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.18674</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25681</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36367</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37362</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32361</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.07504999999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.49593</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.07364</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14091</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.16647</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.28072</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32462</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.5141100000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.49603</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.46724</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.42915</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>-0.04638</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.13245</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2625</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.32873</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.85475</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.34695</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.84414</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.8429099999999999</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.85638</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.40573</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.40348</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.45672</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.46273</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.17545</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.35716</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.84812</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.38111</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.36407</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>1.33824</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.85272</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.8554400000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.84338</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.84584</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.84558</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.8465900000000001</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.84658</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.85127</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.8508300000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.84933</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.84597</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1.48063</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.8459500000000001</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.84593</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.84593</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.38055</v>
+      </c>
+      <c r="H140" t="n">
+        <v>1.35994</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1.37513</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1.37408</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1.37843</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.84622</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.8460800000000001</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.60014</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.5999099999999999</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.8459800000000001</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.8460800000000001</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.84596</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.8461000000000001</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.8460700000000001</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.8459099999999999</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.8461000000000001</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.8462499999999999</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.6000599999999999</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.60011</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.60375</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.60412</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27312</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.22123</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4877</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.4504</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.48422</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.54398</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.54448</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.49945</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.47573</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5025299999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4009</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.48798</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.23421</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.50692</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5184800000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36259</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26568</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.8452799999999999</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.84516</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.84512</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.84562</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.8459</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.84489</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.8463099999999999</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.8459800000000001</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.84624</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.8464400000000001</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.84705</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.84673</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.85229</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.85748</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.8535700000000001</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.2439</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.85361</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.85746</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17949</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06869</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.86446</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21255</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1716</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00541</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26305</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16594</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06152000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05469</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07364</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.16954</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08127</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05942</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.18042</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15527</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.17556</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28752</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26327</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.42555</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41325</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.07698999999999999</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35856</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.50998</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.50762</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.8555499999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.57068</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1.38149</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1.35635</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.84736</v>
+      </c>
+      <c r="N142" t="n">
+        <v>1.35117</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.84563</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1.35663</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.84539</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.84745</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.84682</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.8459500000000001</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.84601</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.8467</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.8455499999999999</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.8459</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.84788</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.8461900000000001</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>1.35562</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.85517</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.84701</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.8544400000000001</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.8580399999999999</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.8583200000000001</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.8574700000000001</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27891</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.85987</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.85089</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.8424199999999999</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01353</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.84205</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.03891</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.83758</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03404</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.005759999999999999</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.0187</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>1.04552</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>1.01719</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.84726</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.84027</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.16282</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.2776</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.84762</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>1.17056</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.8387</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.43732</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.46014</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.43332</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.52425</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.47225</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.44132</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48774</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.42129</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.46534</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.46995</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.47967</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.52027</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5428099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.43531</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.47881</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.47602</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.48077</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.47408</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.8587400000000001</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.45975</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.46854</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.58876</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.6624800000000001</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36632</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.53739</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.44619</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.84588</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.84588</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.8459099999999999</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.84612</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.8461900000000001</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.8466900000000001</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.84615</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.84614</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.8460299999999999</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.84697</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.84646</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14944</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.2169</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.24079</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24506</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11948</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15844</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.02937</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.01155</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04714</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04719</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04608</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04135</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02834</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.8456900000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.10029</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17992</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20694</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12622</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27295</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.04703</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.04802</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.84721</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.15506</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.84629</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.84815</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.84605</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.8499800000000001</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.8462999999999999</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.8468</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.84824</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.84756</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.84762</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.84735</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.44024</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.46086</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.50514</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.53767</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.5096700000000001</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.48049</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.53976</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.53771</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.8536900000000001</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.8542799999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.54516</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.85627</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5430499999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.54434</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.54483</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54347</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.8626200000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.53804</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.50563</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47744</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.47725</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.45532</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.42781</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37588</v>
       </c>
     </row>
   </sheetData>
